--- a/output/pdf_financials_xlsx/OGD.xlsx
+++ b/output/pdf_financials_xlsx/OGD.xlsx
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.293</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.601</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>4.633</v>
@@ -1969,16 +1969,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.293</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.601</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>4.633</v>
@@ -2485,16 +2485,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.484</v>
+        <v>3.149</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.052</v>
+        <v>2.656</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.919</v>
+        <v>1.626</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.543</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>1.166</v>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -33698,7 +33698,11 @@
           <t>General and administrative expenses 2 - 8</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E376" s="5" t="n">
         <v>11.44</v>
       </c>
@@ -34436,7 +34440,11 @@
           <t>General and administrative expenses 2 - 7</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OGD.xlsx
+++ b/output/pdf_financials_xlsx/OGD.xlsx
@@ -1661,40 +1661,40 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.582</v>
+        <v>11.048</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.583</v>
+        <v>10.452</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.583</v>
+        <v>10.8</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>9.576000000000001</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>8.773999999999999</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.29</v>
+        <v>9.988</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.439</v>
+        <v>11.24</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.646</v>
+        <v>10.535</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.321</v>
+        <v>11.143</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.207</v>
+        <v>11.095</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.147</v>
+        <v>10.731</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.078</v>
+        <v>10.075</v>
       </c>
     </row>
     <row r="29">
@@ -1704,40 +1704,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8.225</v>
+        <v>2.241</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.708</v>
+        <v>1.161</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.154</v>
+        <v>10.371</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.867</v>
+        <v>1.709</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.233</v>
+        <v>13.007</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.526</v>
+        <v>6.172</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.679</v>
+        <v>4.122</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.399</v>
+        <v>15.288</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.088</v>
+        <v>7.734</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.636</v>
+        <v>11.524</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.958</v>
+        <v>4.626</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.123</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="30">
@@ -1747,40 +1747,40 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-219.0996270644646</v>
+        <v>59.69632392115077</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-270.855365474339</v>
+        <v>36.11197511664075</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1.509803921568627</v>
+        <v>101.6764705882353</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-97.81176178043019</v>
+        <v>21.24829043889096</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>19.70578650900796</v>
+        <v>60.55118476793445</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-21.64916804813655</v>
+        <v>37.89525388346534</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-51.59919653893697</v>
+        <v>31.84487021013597</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>26.60916707737802</v>
+        <v>75.34746180384427</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1.699205423370677</v>
+        <v>4.25571720995752</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.3482145790217141</v>
+        <v>6.30947296956955</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-3.703565567656273</v>
+        <v>2.875578099358496</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>35.79181840681682</v>
+        <v>71.13813951843863</v>
       </c>
     </row>
     <row r="31">
@@ -4715,40 +4715,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>11.048</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>10.452</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>9.576000000000001</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>8.773999999999999</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>9.988</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>11.24</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>10.535</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>11.143</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>11.095</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>10.731</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>10.075</v>
       </c>
     </row>
     <row r="101">
@@ -5231,40 +5231,40 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.257</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.908</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>1.192</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.996</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>2.623</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>1.178</v>
       </c>
     </row>
     <row r="113">
@@ -16234,7 +16234,11 @@
           <t>Depreciation of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -16296,7 +16300,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -16368,7 +16376,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
@@ -17566,7 +17574,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -18710,7 +18722,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -18772,7 +18788,11 @@
           <t>Depreciation of right-of-use assets 11</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -18844,7 +18864,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -19560,7 +19580,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -19634,7 +19658,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -19710,7 +19738,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -21772,7 +21800,11 @@
           <t>Proceeds from disposal of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -22132,7 +22164,11 @@
           <t>Depreciation of property, plant and equipment 12</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
         <v>10.466</v>
       </c>
@@ -22202,7 +22238,11 @@
           <t>Depreciation of right-of-use assets 13</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -22280,7 +22320,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -23260,7 +23300,11 @@
           <t>Proceeds from disposal of property, plant and equipment 12</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -24006,7 +24050,11 @@
           <t>Proceeds from disposal of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -24750,7 +24798,11 @@
           <t>Proceeds from disposal of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -26996,7 +27048,11 @@
           <t>Proceeds from disposal of property, plant and equipment 12</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E285" s="5" t="n">
         <v>0.355</v>
       </c>

--- a/output/pdf_financials_xlsx/OGD.xlsx
+++ b/output/pdf_financials_xlsx/OGD.xlsx
@@ -1103,10 +1103,10 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>1.993</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>0.251</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.346</v>
@@ -1115,7 +1115,7 @@
         <v>-0.239</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.459</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-3.238</v>
@@ -1124,10 +1124,10 @@
         <v>-1.098</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>4.788</v>
+        <v>3.723</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.508</v>
       </c>
     </row>
     <row r="18">
@@ -1285,15 +1285,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-5.874</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>4.484</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-3.47</v>
@@ -1301,10 +1297,8 @@
       <c r="H20" s="3" t="n">
         <v>-7.357</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="3" t="n">
+        <v>2.294</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-6.647</v>
@@ -1313,12 +1307,10 @@
         <v>-0.669</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-1.317</v>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.382</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>7.537</v>
       </c>
     </row>
     <row r="21">
@@ -1423,10 +1415,10 @@
         <v>-0.429</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-7.867</v>
+        <v>-5.874</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.233</v>
+        <v>4.484</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-3.47</v>
@@ -1435,7 +1427,7 @@
         <v>-7.357</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.753</v>
+        <v>2.294</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-6.647</v>
@@ -1444,10 +1436,10 @@
         <v>-0.669</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-1.317</v>
+        <v>-2.382</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.045</v>
+        <v>7.537</v>
       </c>
     </row>
     <row r="24">
@@ -1578,7 +1570,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46.276471</v>
+        <v>34.552941</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1603,7 +1595,7 @@
         <v>33.45</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>32.925</v>
+        <v>59.55</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -1799,10 +1791,10 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-25.3336723020211</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>5.929600755965037</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-9.067085953878406</v>
@@ -1811,7 +1803,7 @@
         <v>-3.35768474290531</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>51.73574584472964</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-94.98386623643297</v>
@@ -1820,10 +1812,10 @@
         <v>255.9440559440559</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-78.42751842751842</v>
+        <v>-60.98280098280098</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>24.9676455948233</v>
       </c>
     </row>
     <row r="32">
@@ -1842,10 +1834,10 @@
         <v>-4.205882352941177</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-97.81176178043019</v>
+        <v>-73.03245057814249</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>19.70578650900796</v>
+        <v>20.87426097481496</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>-21.30533554368515</v>
@@ -1854,7 +1846,7 @@
         <v>-56.83714462299135</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>23.42533267619517</v>
+        <v>11.30606209955643</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-3.657583694671275</v>
@@ -1863,10 +1855,10 @@
         <v>-0.3662823166124635</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>-0.8186632850962257</v>
+        <v>-1.480680292406385</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>35.5160343669342</v>
+        <v>26.64851677686243</v>
       </c>
     </row>
     <row r="33">
@@ -4681,10 +4673,10 @@
         <v>-0.429</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-7.867</v>
+        <v>-5.874</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>4.233</v>
+        <v>4.484</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-3.47</v>
@@ -4693,7 +4685,7 @@
         <v>-7.357</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>4.753</v>
+        <v>2.294</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-6.647</v>
@@ -4702,10 +4694,10 @@
         <v>-0.669</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-1.317</v>
+        <v>-2.382</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>10.045</v>
+        <v>7.537</v>
       </c>
     </row>
     <row r="100">
@@ -5317,10 +5309,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.116</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.135</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -5329,16 +5321,16 @@
         <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -5363,34 +5355,34 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -5424,19 +5416,19 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.099</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.179</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.309</v>
       </c>
     </row>
     <row r="117">
@@ -5653,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.056</v>
       </c>
     </row>
     <row r="122">
@@ -5972,13 +5964,13 @@
         <v>0</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0</v>
+        <v>-0.163</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>0</v>
+        <v>-0.217</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>0</v>
+        <v>-0.056</v>
       </c>
     </row>
     <row r="129">
@@ -17280,7 +17272,11 @@
           <t>Proceeds from disposal of investments 8</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -17646,7 +17642,11 @@
           <t>Acquisition of intangible assets 13</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -18020,7 +18020,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -18236,7 +18240,11 @@
           <t>Repurchase of common shares 17</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -19436,7 +19444,11 @@
           <t>Acquisition of intangible assets 12</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -20324,7 +20336,11 @@
           <t>Acquisition of intangible assets 11</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -20838,7 +20854,11 @@
           <t>Acquisition of investments 9</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -20910,7 +20930,11 @@
           <t>Proceeds from disposal of investments 9</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -21504,7 +21528,11 @@
           <t>Acquisition of investments 10</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -21654,7 +21682,11 @@
           <t>Proceeds from disposal of investments 10</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -22994,7 +23026,11 @@
           <t>Acquisition of investments 11</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -23070,7 +23106,11 @@
           <t>Proceeds from disposal of investments 11</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -23820,7 +23860,11 @@
           <t>Acquisition of investments 10</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -23896,7 +23940,11 @@
           <t>Proceeds from disposal of investments 10</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -26820,7 +26868,11 @@
           <t>Acquisition of investments 11</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E282" s="5" t="n">
         <v>-0.116</v>
       </c>
@@ -26894,7 +26946,11 @@
           <t>Proceeds from disposal of investments 11</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -27500,7 +27556,11 @@
           <t>Interest revenue 9</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -28134,7 +28194,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -28352,7 +28416,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -31262,7 +31330,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -32802,7 +32874,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -33024,7 +33100,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
